--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 2.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 2.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB2C468-844C-4355-A818-B628870E904B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="5" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -115,7 +114,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
@@ -219,7 +218,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -262,13 +261,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -325,6 +350,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -435,23 +466,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -487,23 +501,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -679,7 +676,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B5C60F9-B610-4ADC-8592-4C80B860454F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -760,7 +757,7 @@
         <v>5</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="25" t="s">
         <v>14</v>
       </c>
       <c r="K3" s="21" t="s">
@@ -784,13 +781,19 @@
       <c r="E4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="18"/>
+      <c r="F4" s="18">
+        <f>INDEX($K$5:$M$7,MATCH(D4,$J$5:$J$7,0),MATCH(E4,$K$4:$M$4,0))</f>
+        <v>2500000</v>
+      </c>
       <c r="G4" s="6">
         <v>3</v>
       </c>
-      <c r="H4" s="19"/>
+      <c r="H4" s="19">
+        <f>F4*G4</f>
+        <v>7500000</v>
+      </c>
       <c r="I4" s="5"/>
-      <c r="J4" s="21"/>
+      <c r="J4" s="26"/>
       <c r="K4" s="14" t="str">
         <f>E4</f>
         <v>TOSHIBA</v>
@@ -818,11 +821,17 @@
       <c r="E5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="18"/>
+      <c r="F5" s="18">
+        <f t="shared" ref="F5:F11" si="0">INDEX($K$5:$M$7,MATCH(D5,$J$5:$J$7,0),MATCH(E5,$K$4:$M$4,0))</f>
+        <v>2450000</v>
+      </c>
       <c r="G5" s="6">
         <v>4</v>
       </c>
-      <c r="H5" s="19"/>
+      <c r="H5" s="19">
+        <f t="shared" ref="H5:H11" si="1">F5*G5</f>
+        <v>9800000</v>
+      </c>
       <c r="I5" s="5"/>
       <c r="J5" s="15" t="s">
         <v>1</v>
@@ -852,11 +861,17 @@
       <c r="E6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="18"/>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>3500000</v>
+      </c>
       <c r="G6" s="6">
         <v>4</v>
       </c>
-      <c r="H6" s="19"/>
+      <c r="H6" s="19">
+        <f t="shared" si="1"/>
+        <v>14000000</v>
+      </c>
       <c r="I6" s="5"/>
       <c r="J6" s="15" t="s">
         <v>2</v>
@@ -886,11 +901,17 @@
       <c r="E7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="18"/>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>2800000</v>
+      </c>
       <c r="G7" s="6">
         <v>3</v>
       </c>
-      <c r="H7" s="19"/>
+      <c r="H7" s="19">
+        <f t="shared" si="1"/>
+        <v>8400000</v>
+      </c>
       <c r="I7" s="5"/>
       <c r="J7" s="15" t="s">
         <v>7</v>
@@ -920,11 +941,17 @@
       <c r="E8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="18"/>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>2350000</v>
+      </c>
       <c r="G8" s="6">
         <v>2</v>
       </c>
-      <c r="H8" s="19"/>
+      <c r="H8" s="19">
+        <f t="shared" si="1"/>
+        <v>4700000</v>
+      </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -946,11 +973,17 @@
       <c r="E9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="18"/>
+      <c r="F9" s="18">
+        <f t="shared" si="0"/>
+        <v>2000000</v>
+      </c>
       <c r="G9" s="6">
         <v>3</v>
       </c>
-      <c r="H9" s="19"/>
+      <c r="H9" s="19">
+        <f t="shared" si="1"/>
+        <v>6000000</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -972,11 +1005,17 @@
       <c r="E10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="18"/>
+      <c r="F10" s="18">
+        <f t="shared" si="0"/>
+        <v>3000000</v>
+      </c>
       <c r="G10" s="6">
         <v>4</v>
       </c>
-      <c r="H10" s="19"/>
+      <c r="H10" s="19">
+        <f t="shared" si="1"/>
+        <v>12000000</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -998,11 +1037,17 @@
       <c r="E11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="18"/>
+      <c r="F11" s="18">
+        <f t="shared" si="0"/>
+        <v>2500000</v>
+      </c>
       <c r="G11" s="6">
         <v>2</v>
       </c>
-      <c r="H11" s="19"/>
+      <c r="H11" s="19">
+        <f t="shared" si="1"/>
+        <v>5000000</v>
+      </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1016,7 +1061,10 @@
       </c>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
-      <c r="E12" s="16"/>
+      <c r="E12" s="16">
+        <f>SUM(H4:H11)</f>
+        <v>67400000</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="2"/>
       <c r="H12" s="1"/>
@@ -1033,7 +1081,10 @@
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
-      <c r="E13" s="17"/>
+      <c r="E13" s="17">
+        <f>SUMIFS(G4:G11,D4:D11,"TV",E4:E11,"TOSHIBA")</f>
+        <v>5</v>
+      </c>
       <c r="G13" s="23" t="s">
         <v>28</v>
       </c>
@@ -1050,7 +1101,10 @@
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
-      <c r="E14" s="17"/>
+      <c r="E14" s="17">
+        <f>SUMIF(D4:D11,"AC",G4:G11)</f>
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1063,7 +1117,7 @@
     <mergeCell ref="J13:L13"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J13" r:id="rId1" xr:uid="{11A26802-1549-46B2-8EE7-41AE86AD0510}"/>
+    <hyperlink ref="J13" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 2.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 2.xlsx
@@ -1,20 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE85AAE4-426E-4CAE-AF0F-B55B8AEE4B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="5" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -114,7 +126,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
@@ -218,7 +230,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -261,39 +273,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -350,12 +336,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -391,9 +371,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -431,9 +411,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -468,7 +448,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -503,7 +483,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -676,7 +656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B5C60F9-B610-4ADC-8592-4C80B860454F}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -757,7 +737,7 @@
         <v>5</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="21" t="s">
         <v>14</v>
       </c>
       <c r="K3" s="21" t="s">
@@ -793,7 +773,7 @@
         <v>7500000</v>
       </c>
       <c r="I4" s="5"/>
-      <c r="J4" s="26"/>
+      <c r="J4" s="21"/>
       <c r="K4" s="14" t="str">
         <f>E4</f>
         <v>TOSHIBA</v>
@@ -1117,7 +1097,7 @@
     <mergeCell ref="J13:L13"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J13" r:id="rId1"/>
+    <hyperlink ref="J13" r:id="rId1" xr:uid="{11A26802-1549-46B2-8EE7-41AE86AD0510}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
